--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260729.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260729.xlsx
@@ -601,88 +601,88 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>202608WTX</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>115/08台股期貨</t>
+          <t>聯詠科技</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>9,852,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.86%</t>
+          <t>3.92%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>202608WTX</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>聯詠科技</t>
+          <t>115/08台股期貨</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>9,852,000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>3.82%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>華碩電腦</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>5,820,000</t>
+          <t>5,759,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.46%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>華碩電腦</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>5,759,000</t>
+          <t>5,820,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.28%</t>
+          <t>3.39%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.11%</t>
         </is>
       </c>
     </row>
@@ -726,117 +726,117 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.07%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>20,517,000</t>
+          <t>9,790,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>3.04%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>3,801,000</t>
+          <t>20,517,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.92%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>9,544,000</t>
+          <t>3,801,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>24,881,000</t>
+          <t>32,918,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>32,918,000</t>
+          <t>24,881,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
@@ -858,29 +858,29 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>6,485,000</t>
+          <t>19,313,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.58%</t>
         </is>
       </c>
     </row>
@@ -902,29 +902,29 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.51%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>19,313,000</t>
+          <t>6,485,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.51%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
@@ -990,29 +990,29 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>4,126,000</t>
+          <t>2,820,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
@@ -1034,68 +1034,68 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2,820,000</t>
+          <t>4,126,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>15,056,000</t>
+          <t>14,134,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>17,369,000</t>
+          <t>15,056,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1122,95 +1122,95 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>3,862,000</t>
+          <t>40,734,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>2,498,166,473</t>
+          <t>3,862,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>14,134,000</t>
+          <t>17,369,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>40,734,000</t>
+          <t>2,282,973,495</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
@@ -1271,29 +1271,29 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>6,220,000</t>
+          <t>6,546,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>3,498,000</t>
+          <t>518,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,154 +1305,154 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>5,666,000</t>
+          <t>1,976,545,322</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>14,120,000</t>
+          <t>5,666,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>518,000</t>
+          <t>3,498,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>23,205,000</t>
+          <t>14,120,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.52%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,925,945,322</t>
+          <t>23,205,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>至上電子</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>16,505,000</t>
+          <t>22,613,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>至上電子</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>22,613,000</t>
+          <t>16,505,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -1491,56 +1491,56 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>8,771,000</t>
+          <t>8,951,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>8,715,000</t>
+          <t>1,575,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>1,575,000</t>
+          <t>8,715,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
@@ -1562,68 +1562,68 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>2,088,000</t>
+          <t>47,231,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>47,231,000</t>
+          <t>2,088,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>8,865,000</t>
+          <t>48,929,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,66 +1635,66 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>原相科技</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>48,929,000</t>
+          <t>6,330,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>原相科技</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>6,330,000</t>
+          <t>8,865,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>16,588,000</t>
+          <t>18,691,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
@@ -1723,22 +1723,22 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>17,290,000</t>
+          <t>16,588,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-97,517,925</t>
+          <t>-37,677,105</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.03%</t>
         </is>
       </c>
     </row>
